--- a/plantillas_excel/55_extraccion_vigencias.xlsx
+++ b/plantillas_excel/55_extraccion_vigencias.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
         </is>
       </c>
     </row>
